--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1134,6 +1134,232 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132007143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96636</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>662413</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6557013</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>4 st</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132007141</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92279</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>662426</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6557028</v>
+      </c>
+      <c r="S7" t="n">
+        <v>18</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96636</v>
+        <v>96637</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92280</v>
+        <v>92285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96642</v>
+        <v>96644</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92285</v>
+        <v>92287</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96644</v>
+        <v>96680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92287</v>
+        <v>92323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92328</v>
+        <v>92331</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96688</v>
+        <v>96696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92331</v>
+        <v>92337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96696</v>
+        <v>96706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92337</v>
+        <v>92347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -1139,7 +1139,7 @@
         <v>132007143</v>
       </c>
       <c r="B6" t="n">
-        <v>96706</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,55 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>80689000</v>
+        <v>80688748</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>889</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Uringe, Srm</t>
+          <t>Rosenhill, Botkyrka kommun, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>662406.4514923706</v>
+        <v>662361</v>
       </c>
       <c r="R2" t="n">
-        <v>6557020.16404229</v>
+        <v>6557056</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,19 +744,9 @@
           <t>2019-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,56 +766,42 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>88013939</v>
+        <v>91204868</v>
       </c>
       <c r="B3" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6031</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,13 +809,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>662433.8575293025</v>
+        <v>662377</v>
       </c>
       <c r="R3" t="n">
-        <v>6557029.553963899</v>
+        <v>6557056</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +839,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-02-27</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Små vintertaggingar uppe på grenar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,75 +864,62 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Tiina Laantee</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
+          <t>Tiina Laantee, Thomas Strid</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96354933</v>
+        <v>80689000</v>
       </c>
       <c r="B4" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Botkyrka, Srm</t>
+          <t>Uringe, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>662392</v>
+        <v>662406</v>
       </c>
       <c r="R4" t="n">
         <v>6557020</v>
       </c>
       <c r="S4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -991,12 +943,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-09-28</t>
+          <t>2019-11-01</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,27 +963,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tiina Laantee</t>
+          <t>Thomas Strid, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>103857612</v>
+        <v>132007143</v>
       </c>
       <c r="B5" t="n">
-        <v>89789</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96783</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,38 +986,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Uringeskogen, Srm</t>
+          <t>Hagaberg, Hagaberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>662430.4243713052</v>
+        <v>662413</v>
       </c>
       <c r="R5" t="n">
-        <v>6557037.631952946</v>
+        <v>6557013</v>
       </c>
       <c r="S5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,22 +1044,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-01</t>
+          <t>2026-03-29</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 st</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,22 +1079,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Strid, Tiina Laantee</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132007143</v>
+        <v>103857612</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,41 +1102,38 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hagaberg, Hagaberg, Srm</t>
+          <t>Uringeskogen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>662413</v>
+        <v>662430</v>
       </c>
       <c r="R6" t="n">
-        <v>6557013</v>
+        <v>6557038</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1205,27 +1157,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:22</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 st</t>
+          <t>2022-10-01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,12 +1177,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Thomas Strid, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1255,7 +1192,7 @@
         <v>132007141</v>
       </c>
       <c r="B7" t="n">
-        <v>92348</v>
+        <v>92385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1360,6 +1297,806 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>96354933</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>662392</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6557020</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-09-28</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>88013939</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Uringe, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>662434</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6557030</v>
+      </c>
+      <c r="S9" t="n">
+        <v>12</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113208399</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92567</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Uringe, Uringe, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>662379</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6556996</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Thomas Strid</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Thomas Strid, Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>94478309</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57754</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>102118</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nattskärra</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Caprimulgus europaeus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Uringeskogen, Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>662368</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6557006</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-06-26</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>02:35</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tiina Laantee, Thomas Strid, Roger Kaufmann, Marie Teilmann</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>92453790</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>662399</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6557017</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-04-16</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>92673596</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Uringeskogen, Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>662518</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6557105</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-04-23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-04-23</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tiina Laantee</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132007128</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Hagaberg, Hagaberg, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>662376</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6557006</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 12818-2026 artfynd.xlsx
+++ b/artfynd/A 12818-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80688748</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91204868</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -972,6 +987,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80689000</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132007143</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,6 +1211,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103857612</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132007141</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96354933</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1510,6 +1550,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88013939</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1617,6 +1662,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113208399</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1739,6 +1789,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94478309</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1865,6 +1920,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92453790</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92673596</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2096,8 +2161,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132007128</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>